--- a/docs/xlsx/jobs-2026-10-10.xlsx
+++ b/docs/xlsx/jobs-2026-10-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,103 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Coral Reef Montessori Academy</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2f7d28cf3564a3486003767fa419039-administrative-assistant-coral-reef-montessori-academy-miami</t>
+  </si>
+  <si>
+    <t>Direct Support Professional- Adult Day Program</t>
+  </si>
+  <si>
+    <t>Tavon Learning Center</t>
+  </si>
+  <si>
+    <t>Issaquah, Washington</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7a6ced6c17347d89f0767b4709075a3-direct-support-professional-adult-day-program-tavon-learning-center-issaquah</t>
+  </si>
+  <si>
+    <t>Grant Writer</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 15.00 - 18.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e233d14573844927875394bfadbd4f8a-grant-writer-coral-reef-montessori-academy-miami</t>
+  </si>
+  <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN IRVINE!</t>
+  </si>
+  <si>
+    <t>UNITE HERE! Local 11</t>
+  </si>
+  <si>
+    <t>Irvine, California</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0223f1cfd70441ac801455b48a6abff9-join-a-progressive-campaign-in-irvine-unite-here-local-11-irvine</t>
+  </si>
+  <si>
+    <t>Resonance Technical Fellow</t>
+  </si>
+  <si>
+    <t>Resonance</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/693463403dc44402af1541cdc124f2ee-resonance-technical-fellow-resonance-san-francisco</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +144,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +170,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -514,7 +609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +648,130 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-10.xlsx
+++ b/docs/xlsx/jobs-2026-10-10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="57">
   <si>
     <t>Title</t>
   </si>
@@ -61,6 +61,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a2f7d28cf3564a3486003767fa419039-administrative-assistant-coral-reef-montessori-academy-miami</t>
   </si>
   <si>
+    <t>Community Organizer</t>
+  </si>
+  <si>
+    <t>My Eden Voice</t>
+  </si>
+  <si>
+    <t>Ashland, California</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 73000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4fd19c5ac58941c0ad12b23deb56a573-community-organizer-my-eden-voice-ashland</t>
+  </si>
+  <si>
     <t>Direct Support Professional- Adult Day Program</t>
   </si>
   <si>
@@ -128,6 +146,45 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/693463403dc44402af1541cdc124f2ee-resonance-technical-fellow-resonance-san-francisco</t>
+  </si>
+  <si>
+    <t>TerraForge Program Manager</t>
+  </si>
+  <si>
+    <t>VertueLab</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 33.65 - 34.61/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Economic Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bdb2676be01a4b278336951da1c01ee5-terraforge-program-manager-vertuelab-portland</t>
+  </si>
+  <si>
+    <t>U.S. Managing Director</t>
+  </si>
+  <si>
+    <t>Foundation for African Medicine and Education</t>
+  </si>
+  <si>
+    <t>Cambridge, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/780fd450caf54c0d9c66eb58467f3546-us-managing-director-foundation-for-african-medicine-and-education-cambridge</t>
   </si>
 </sst>
 </file>
@@ -609,7 +666,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -699,56 +756,56 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
       </c>
       <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
       </c>
       <c r="D6" t="s">
         <v>34</v>
@@ -761,6 +818,75 @@
       </c>
       <c r="H6" s="2" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -771,6 +897,9 @@
     <hyperlink ref="H4" r:id="rId3"/>
     <hyperlink ref="H5" r:id="rId4"/>
     <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
